--- a/04_DESIGN_TABLES/DesignTable_1724.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1724.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,26 @@
           <t>$COMMENT</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L@DRIVE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SHANKD@REF</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>O@DRIVE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -468,12 +488,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -489,6 +509,20 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
